--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124983689</v>
+        <v>124983283</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611306</v>
+        <v>611235</v>
       </c>
       <c r="R2" t="n">
-        <v>6954281</v>
+        <v>6954362</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124985090</v>
+        <v>124983689</v>
       </c>
       <c r="B4" t="n">
-        <v>96227</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611380</v>
+        <v>611306</v>
       </c>
       <c r="R4" t="n">
-        <v>6954314</v>
+        <v>6954281</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124984680</v>
+        <v>124983851</v>
       </c>
       <c r="B5" t="n">
-        <v>96227</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611345</v>
+        <v>611282</v>
       </c>
       <c r="R5" t="n">
-        <v>6954282</v>
+        <v>6954281</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124983934</v>
+        <v>124984680</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,42 +1100,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611281</v>
+        <v>611345</v>
       </c>
       <c r="R6" t="n">
-        <v>6954283</v>
+        <v>6954282</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124983283</v>
+        <v>124983934</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,38 +1202,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611235</v>
+        <v>611281</v>
       </c>
       <c r="R7" t="n">
-        <v>6954362</v>
+        <v>6954283</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1291,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124983851</v>
+        <v>124983255</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,39 +1312,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611282</v>
+        <v>611239</v>
       </c>
       <c r="R8" t="n">
-        <v>6954281</v>
+        <v>6954361</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124983255</v>
+        <v>124985090</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>96227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,38 +1410,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611239</v>
+        <v>611380</v>
       </c>
       <c r="R9" t="n">
-        <v>6954361</v>
+        <v>6954314</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124983283</v>
+        <v>124983689</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611235</v>
+        <v>611306</v>
       </c>
       <c r="R2" t="n">
-        <v>6954362</v>
+        <v>6954281</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124984511</v>
+        <v>124983934</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -810,17 +810,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611365</v>
+        <v>611281</v>
       </c>
       <c r="R3" t="n">
-        <v>6954258</v>
+        <v>6954283</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124983689</v>
+        <v>124984511</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611306</v>
+        <v>611365</v>
       </c>
       <c r="R4" t="n">
-        <v>6954281</v>
+        <v>6954258</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1088,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124984680</v>
+        <v>124985090</v>
       </c>
       <c r="B6" t="n">
         <v>96227</v>
@@ -1128,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611345</v>
+        <v>611380</v>
       </c>
       <c r="R6" t="n">
-        <v>6954282</v>
+        <v>6954314</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124983934</v>
+        <v>124983283</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,42 +1206,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611281</v>
+        <v>611235</v>
       </c>
       <c r="R7" t="n">
-        <v>6954283</v>
+        <v>6954362</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124985090</v>
+        <v>124984680</v>
       </c>
       <c r="B9" t="n">
         <v>96227</v>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611380</v>
+        <v>611345</v>
       </c>
       <c r="R9" t="n">
-        <v>6954314</v>
+        <v>6954282</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124983283</v>
+        <v>124983255</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611235</v>
+        <v>611239</v>
       </c>
       <c r="R7" t="n">
-        <v>6954362</v>
+        <v>6954361</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124983255</v>
+        <v>124983283</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611239</v>
+        <v>611235</v>
       </c>
       <c r="R8" t="n">
-        <v>6954361</v>
+        <v>6954362</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124983689</v>
+        <v>124983934</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611306</v>
+        <v>611281</v>
       </c>
       <c r="R2" t="n">
-        <v>6954281</v>
+        <v>6954283</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124983934</v>
+        <v>124983283</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611281</v>
+        <v>611235</v>
       </c>
       <c r="R3" t="n">
-        <v>6954283</v>
+        <v>6954362</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124984511</v>
+        <v>124983851</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +895,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611365</v>
+        <v>611282</v>
       </c>
       <c r="R4" t="n">
-        <v>6954258</v>
+        <v>6954281</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124983851</v>
+        <v>124984511</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,43 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611282</v>
+        <v>611365</v>
       </c>
       <c r="R5" t="n">
-        <v>6954281</v>
+        <v>6954258</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124985090</v>
+        <v>124983255</v>
       </c>
       <c r="B6" t="n">
-        <v>96227</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,38 +1104,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611380</v>
+        <v>611239</v>
       </c>
       <c r="R6" t="n">
-        <v>6954314</v>
+        <v>6954361</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124983255</v>
+        <v>124985090</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>96227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,38 +1206,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611239</v>
+        <v>611380</v>
       </c>
       <c r="R7" t="n">
-        <v>6954361</v>
+        <v>6954314</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124983283</v>
+        <v>124984680</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>96227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,34 +1312,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611235</v>
+        <v>611345</v>
       </c>
       <c r="R8" t="n">
-        <v>6954362</v>
+        <v>6954282</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124984680</v>
+        <v>124983689</v>
       </c>
       <c r="B9" t="n">
-        <v>96227</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611345</v>
+        <v>611306</v>
       </c>
       <c r="R9" t="n">
-        <v>6954282</v>
+        <v>6954281</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124984511</v>
+        <v>124983255</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611365</v>
+        <v>611239</v>
       </c>
       <c r="R5" t="n">
-        <v>6954258</v>
+        <v>6954361</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124983255</v>
+        <v>124984511</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,38 +1104,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611239</v>
+        <v>611365</v>
       </c>
       <c r="R6" t="n">
-        <v>6954361</v>
+        <v>6954258</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124983934</v>
+        <v>124984511</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,21 +708,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611281</v>
+        <v>611365</v>
       </c>
       <c r="R2" t="n">
-        <v>6954283</v>
+        <v>6954258</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124983283</v>
+        <v>124983934</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611235</v>
+        <v>611281</v>
       </c>
       <c r="R3" t="n">
-        <v>6954362</v>
+        <v>6954283</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124983851</v>
+        <v>124984680</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>96227</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,43 +895,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611282</v>
+        <v>611345</v>
       </c>
       <c r="R4" t="n">
-        <v>6954281</v>
+        <v>6954282</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1092,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124984511</v>
+        <v>124985090</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1099,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611365</v>
+        <v>611380</v>
       </c>
       <c r="R6" t="n">
-        <v>6954258</v>
+        <v>6954314</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124985090</v>
+        <v>124983689</v>
       </c>
       <c r="B7" t="n">
-        <v>96227</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1201,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611380</v>
+        <v>611306</v>
       </c>
       <c r="R7" t="n">
-        <v>6954314</v>
+        <v>6954281</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124984680</v>
+        <v>124983283</v>
       </c>
       <c r="B8" t="n">
-        <v>96227</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,34 +1307,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611345</v>
+        <v>611235</v>
       </c>
       <c r="R8" t="n">
-        <v>6954282</v>
+        <v>6954362</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124983689</v>
+        <v>124983851</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,31 +1409,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611306</v>
+        <v>611282</v>
       </c>
       <c r="R9" t="n">
         <v>6954281</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124984511</v>
+        <v>124983851</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611365</v>
+        <v>611282</v>
       </c>
       <c r="R2" t="n">
-        <v>6954258</v>
+        <v>6954281</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124983934</v>
+        <v>124985090</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611281</v>
+        <v>611380</v>
       </c>
       <c r="R3" t="n">
-        <v>6954283</v>
+        <v>6954314</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124984680</v>
+        <v>124983255</v>
       </c>
       <c r="B4" t="n">
-        <v>96227</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611345</v>
+        <v>611239</v>
       </c>
       <c r="R4" t="n">
-        <v>6954282</v>
+        <v>6954361</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124983255</v>
+        <v>124983283</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611239</v>
+        <v>611235</v>
       </c>
       <c r="R5" t="n">
-        <v>6954361</v>
+        <v>6954362</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1087,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124985090</v>
+        <v>124983689</v>
       </c>
       <c r="B6" t="n">
-        <v>96227</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611380</v>
+        <v>611306</v>
       </c>
       <c r="R6" t="n">
-        <v>6954314</v>
+        <v>6954281</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124983689</v>
+        <v>124983934</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,38 +1202,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611306</v>
+        <v>611281</v>
       </c>
       <c r="R7" t="n">
-        <v>6954281</v>
+        <v>6954283</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1291,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124983283</v>
+        <v>124984511</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,38 +1308,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611235</v>
+        <v>611365</v>
       </c>
       <c r="R8" t="n">
-        <v>6954362</v>
+        <v>6954258</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124983851</v>
+        <v>124984680</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>96227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,43 +1410,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611282</v>
+        <v>611345</v>
       </c>
       <c r="R9" t="n">
-        <v>6954281</v>
+        <v>6954282</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124983851</v>
+        <v>124984511</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611282</v>
+        <v>611365</v>
       </c>
       <c r="R2" t="n">
-        <v>6954281</v>
+        <v>6954258</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124985090</v>
+        <v>124983283</v>
       </c>
       <c r="B3" t="n">
-        <v>96227</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611380</v>
+        <v>611235</v>
       </c>
       <c r="R3" t="n">
-        <v>6954314</v>
+        <v>6954362</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124983255</v>
+        <v>124983851</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611239</v>
+        <v>611282</v>
       </c>
       <c r="R4" t="n">
-        <v>6954361</v>
+        <v>6954281</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124983283</v>
+        <v>124984680</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>96227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611235</v>
+        <v>611345</v>
       </c>
       <c r="R5" t="n">
-        <v>6954362</v>
+        <v>6954282</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124983689</v>
+        <v>124985090</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>96227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611306</v>
+        <v>611380</v>
       </c>
       <c r="R6" t="n">
-        <v>6954281</v>
+        <v>6954314</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124983934</v>
+        <v>124983689</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,42 +1202,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611281</v>
+        <v>611306</v>
       </c>
       <c r="R7" t="n">
-        <v>6954283</v>
+        <v>6954281</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124984511</v>
+        <v>124983255</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,38 +1304,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611365</v>
+        <v>611239</v>
       </c>
       <c r="R8" t="n">
-        <v>6954258</v>
+        <v>6954361</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124984680</v>
+        <v>124983934</v>
       </c>
       <c r="B9" t="n">
-        <v>96227</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,38 +1406,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611345</v>
+        <v>611281</v>
       </c>
       <c r="R9" t="n">
-        <v>6954282</v>
+        <v>6954283</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124984511</v>
+        <v>124984680</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611365</v>
+        <v>611345</v>
       </c>
       <c r="R2" t="n">
-        <v>6954258</v>
+        <v>6954282</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124983283</v>
+        <v>124983689</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611235</v>
+        <v>611306</v>
       </c>
       <c r="R3" t="n">
-        <v>6954362</v>
+        <v>6954281</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124983851</v>
+        <v>124983934</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,31 +891,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -924,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611282</v>
+        <v>611281</v>
       </c>
       <c r="R4" t="n">
-        <v>6954281</v>
+        <v>6954283</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124984680</v>
+        <v>124983283</v>
       </c>
       <c r="B5" t="n">
-        <v>96227</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +1001,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611345</v>
+        <v>611235</v>
       </c>
       <c r="R5" t="n">
-        <v>6954282</v>
+        <v>6954362</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124985090</v>
+        <v>124984511</v>
       </c>
       <c r="B6" t="n">
-        <v>96227</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1099,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611380</v>
+        <v>611365</v>
       </c>
       <c r="R6" t="n">
-        <v>6954314</v>
+        <v>6954258</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124983689</v>
+        <v>124983851</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,31 +1205,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611306</v>
+        <v>611282</v>
       </c>
       <c r="R7" t="n">
         <v>6954281</v>
@@ -1292,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124983255</v>
+        <v>124985090</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>96227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,38 +1308,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611239</v>
+        <v>611380</v>
       </c>
       <c r="R8" t="n">
-        <v>6954361</v>
+        <v>6954314</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124983934</v>
+        <v>124983255</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,42 +1410,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611281</v>
+        <v>611239</v>
       </c>
       <c r="R9" t="n">
-        <v>6954283</v>
+        <v>6954361</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124984680</v>
+        <v>124983689</v>
       </c>
       <c r="B2" t="n">
-        <v>96227</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611345</v>
+        <v>611306</v>
       </c>
       <c r="R2" t="n">
-        <v>6954282</v>
+        <v>6954281</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124983689</v>
+        <v>124983255</v>
       </c>
       <c r="B3" t="n">
         <v>91299</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611306</v>
+        <v>611239</v>
       </c>
       <c r="R3" t="n">
-        <v>6954281</v>
+        <v>6954361</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124983934</v>
+        <v>124984511</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -912,21 +912,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611281</v>
+        <v>611365</v>
       </c>
       <c r="R4" t="n">
-        <v>6954283</v>
+        <v>6954258</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124983283</v>
+        <v>124984680</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>96227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611235</v>
+        <v>611345</v>
       </c>
       <c r="R5" t="n">
-        <v>6954362</v>
+        <v>6954282</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1087,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124984511</v>
+        <v>124983934</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1120,17 +1116,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611365</v>
+        <v>611281</v>
       </c>
       <c r="R6" t="n">
-        <v>6954258</v>
+        <v>6954283</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124983851</v>
+        <v>124983283</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,43 +1201,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611282</v>
+        <v>611235</v>
       </c>
       <c r="R7" t="n">
-        <v>6954281</v>
+        <v>6954362</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1398,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124983255</v>
+        <v>124983851</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,34 +1409,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611239</v>
+        <v>611282</v>
       </c>
       <c r="R9" t="n">
-        <v>6954361</v>
+        <v>6954281</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124983689</v>
+        <v>124983283</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611306</v>
+        <v>611235</v>
       </c>
       <c r="R2" t="n">
-        <v>6954281</v>
+        <v>6954362</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124983255</v>
+        <v>124983851</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611239</v>
+        <v>611282</v>
       </c>
       <c r="R3" t="n">
-        <v>6954361</v>
+        <v>6954281</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124984680</v>
+        <v>124983934</v>
       </c>
       <c r="B5" t="n">
-        <v>96227</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +998,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611345</v>
+        <v>611281</v>
       </c>
       <c r="R5" t="n">
-        <v>6954282</v>
+        <v>6954283</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124983934</v>
+        <v>124984680</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,42 +1104,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611281</v>
+        <v>611345</v>
       </c>
       <c r="R6" t="n">
-        <v>6954283</v>
+        <v>6954282</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124983283</v>
+        <v>124985090</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>96227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,34 +1210,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611235</v>
+        <v>611380</v>
       </c>
       <c r="R7" t="n">
-        <v>6954362</v>
+        <v>6954314</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1291,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124985090</v>
+        <v>124983689</v>
       </c>
       <c r="B8" t="n">
-        <v>96227</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611380</v>
+        <v>611306</v>
       </c>
       <c r="R8" t="n">
-        <v>6954314</v>
+        <v>6954281</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124983851</v>
+        <v>124983255</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,39 +1414,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611282</v>
+        <v>611239</v>
       </c>
       <c r="R9" t="n">
-        <v>6954281</v>
+        <v>6954361</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124983283</v>
+        <v>124983255</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611235</v>
+        <v>611239</v>
       </c>
       <c r="R2" t="n">
-        <v>6954362</v>
+        <v>6954361</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124984511</v>
+        <v>124983689</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611365</v>
+        <v>611306</v>
       </c>
       <c r="R4" t="n">
-        <v>6954258</v>
+        <v>6954281</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124983934</v>
+        <v>124984680</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,42 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611281</v>
+        <v>611345</v>
       </c>
       <c r="R5" t="n">
-        <v>6954283</v>
+        <v>6954282</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1092,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124984680</v>
+        <v>124984511</v>
       </c>
       <c r="B6" t="n">
-        <v>96227</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611345</v>
+        <v>611365</v>
       </c>
       <c r="R6" t="n">
-        <v>6954282</v>
+        <v>6954258</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124985090</v>
+        <v>124983283</v>
       </c>
       <c r="B7" t="n">
-        <v>96227</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,34 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611380</v>
+        <v>611235</v>
       </c>
       <c r="R7" t="n">
-        <v>6954314</v>
+        <v>6954362</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124983689</v>
+        <v>124985090</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>96227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611306</v>
+        <v>611380</v>
       </c>
       <c r="R8" t="n">
-        <v>6954281</v>
+        <v>6954314</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124983255</v>
+        <v>124983934</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,38 +1406,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611239</v>
+        <v>611281</v>
       </c>
       <c r="R9" t="n">
-        <v>6954361</v>
+        <v>6954283</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124983255</v>
+        <v>124983851</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611239</v>
+        <v>611282</v>
       </c>
       <c r="R2" t="n">
-        <v>6954361</v>
+        <v>6954281</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124983851</v>
+        <v>124984511</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611282</v>
+        <v>611365</v>
       </c>
       <c r="R3" t="n">
-        <v>6954281</v>
+        <v>6954258</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124983689</v>
+        <v>124983255</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>91459</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611306</v>
+        <v>611239</v>
       </c>
       <c r="R4" t="n">
-        <v>6954281</v>
+        <v>6954361</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124984680</v>
+        <v>124983934</v>
       </c>
       <c r="B5" t="n">
-        <v>96227</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +998,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611345</v>
+        <v>611281</v>
       </c>
       <c r="R5" t="n">
-        <v>6954282</v>
+        <v>6954283</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124984511</v>
+        <v>124983689</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91459</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611365</v>
+        <v>611306</v>
       </c>
       <c r="R6" t="n">
-        <v>6954258</v>
+        <v>6954281</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124983283</v>
+        <v>124984680</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>96395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,34 +1210,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611235</v>
+        <v>611345</v>
       </c>
       <c r="R7" t="n">
-        <v>6954362</v>
+        <v>6954282</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1295,7 +1299,7 @@
         <v>124985090</v>
       </c>
       <c r="B8" t="n">
-        <v>96227</v>
+        <v>96395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124983934</v>
+        <v>124983283</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,42 +1410,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611281</v>
+        <v>611235</v>
       </c>
       <c r="R9" t="n">
-        <v>6954283</v>
+        <v>6954362</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124983851</v>
+        <v>124984511</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611282</v>
+        <v>611365</v>
       </c>
       <c r="R2" t="n">
-        <v>6954281</v>
+        <v>6954258</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124984511</v>
+        <v>124983851</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611365</v>
+        <v>611282</v>
       </c>
       <c r="R3" t="n">
-        <v>6954258</v>
+        <v>6954281</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124984511</v>
+        <v>124983255</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>91459</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611365</v>
+        <v>611239</v>
       </c>
       <c r="R2" t="n">
-        <v>6954258</v>
+        <v>6954361</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124983255</v>
+        <v>124983689</v>
       </c>
       <c r="B4" t="n">
         <v>91459</v>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611239</v>
+        <v>611306</v>
       </c>
       <c r="R4" t="n">
-        <v>6954361</v>
+        <v>6954281</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124983689</v>
+        <v>124983283</v>
       </c>
       <c r="B6" t="n">
-        <v>91459</v>
+        <v>91131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,38 +1104,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
+          <t>Åsinget, Åsinget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611306</v>
+        <v>611235</v>
       </c>
       <c r="R6" t="n">
-        <v>6954281</v>
+        <v>6954362</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124985090</v>
+        <v>124984511</v>
       </c>
       <c r="B8" t="n">
-        <v>96395</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611380</v>
+        <v>611365</v>
       </c>
       <c r="R8" t="n">
-        <v>6954314</v>
+        <v>6954258</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124983283</v>
+        <v>124985090</v>
       </c>
       <c r="B9" t="n">
-        <v>91131</v>
+        <v>96395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,34 +1414,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åsinget, Åsinget, Mpd</t>
+          <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611235</v>
+        <v>611380</v>
       </c>
       <c r="R9" t="n">
-        <v>6954362</v>
+        <v>6954314</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124984511</v>
+        <v>124985090</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>96395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611365</v>
+        <v>611380</v>
       </c>
       <c r="R8" t="n">
-        <v>6954258</v>
+        <v>6954314</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124985090</v>
+        <v>124984511</v>
       </c>
       <c r="B9" t="n">
-        <v>96395</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611380</v>
+        <v>611365</v>
       </c>
       <c r="R9" t="n">
-        <v>6954314</v>
+        <v>6954258</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124983255</v>
+        <v>124983283</v>
       </c>
       <c r="B2" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611239</v>
+        <v>611235</v>
       </c>
       <c r="R2" t="n">
-        <v>6954361</v>
+        <v>6954362</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124983851</v>
+        <v>124983689</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,36 +783,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611282</v>
+        <v>611306</v>
       </c>
       <c r="R3" t="n">
         <v>6954281</v>
@@ -884,50 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124983689</v>
+        <v>124983934</v>
       </c>
       <c r="B4" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611306</v>
+        <v>611281</v>
       </c>
       <c r="R4" t="n">
-        <v>6954281</v>
+        <v>6954283</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,16 +970,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124983934</v>
+        <v>124984511</v>
       </c>
       <c r="B5" t="n">
         <v>98269</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>VU</t>
@@ -1019,21 +998,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611281</v>
+        <v>611365</v>
       </c>
       <c r="R5" t="n">
-        <v>6954283</v>
+        <v>6954258</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1092,37 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124983283</v>
+        <v>124983255</v>
       </c>
       <c r="B6" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611235</v>
+        <v>611239</v>
       </c>
       <c r="R6" t="n">
-        <v>6954362</v>
+        <v>6954361</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,50 +1164,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124984680</v>
+        <v>124983851</v>
       </c>
       <c r="B7" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611345</v>
+        <v>611282</v>
       </c>
       <c r="R7" t="n">
-        <v>6954282</v>
+        <v>6954281</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,16 +1266,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124985090</v>
+        <v>124984680</v>
       </c>
       <c r="B8" t="n">
         <v>96395</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1336,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611380</v>
+        <v>611345</v>
       </c>
       <c r="R8" t="n">
-        <v>6954314</v>
+        <v>6954282</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,37 +1363,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124984511</v>
+        <v>124985090</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611365</v>
+        <v>611380</v>
       </c>
       <c r="R9" t="n">
-        <v>6954258</v>
+        <v>6954314</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>124983851</v>
       </c>
       <c r="B7" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>124983851</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>124983851</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>124983851</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>124983851</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11397-2025 artfynd.xlsx
+++ b/artfynd/A 11397-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>124983851</v>
       </c>
       <c r="B7" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
